--- a/ΠΕΛΑΤΕΣ.xlsx
+++ b/ΠΕΛΑΤΕΣ.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="630" yWindow="600" windowWidth="26535" windowHeight="8640"/>
-  </bookViews>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr date1904="0"/>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Ημ/νία Καταχώρησης</t>
   </si>
@@ -61,58 +56,553 @@
     <t>User_Rejections</t>
   </si>
   <si>
-    <t>23/4/2026</t>
+    <t>14/5/2026</t>
   </si>
   <si>
     <t>Τέλος Καταμέτρησης</t>
   </si>
   <si>
-    <t>SH(C350)-0000011809</t>
+    <t>SH(C)-0000028594</t>
+  </si>
+  <si>
+    <t>001 Έδρα</t>
+  </si>
+  <si>
+    <t>802286216</t>
+  </si>
+  <si>
+    <t>FKNG ΜΟΝΟΠΡΟΣΩΠΗ Ι Κ Ε</t>
+  </si>
+  <si>
+    <t>Α.ΙΩΑΝΝΙΔΗ ΚΑΙ ΚΛΕΟΠΑΤΡΑΣ</t>
+  </si>
+  <si>
+    <t>ΚΩΣ</t>
+  </si>
+  <si>
+    <t>ΨΥΓΕΙΟ</t>
+  </si>
+  <si>
+    <t>ΟΧΙ</t>
+  </si>
+  <si>
+    <t>Μέτρηση</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019472</t>
+  </si>
+  <si>
+    <t>Κ340 Ρέντη</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019471</t>
+  </si>
+  <si>
+    <t>ΞΗΡΟ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012464</t>
   </si>
   <si>
     <t>Κ350 Μοσχάτο ΙΙ</t>
   </si>
   <si>
-    <t>ΧΑΝΙΑ</t>
-  </si>
-  <si>
-    <t>ΞΗΡΟ</t>
-  </si>
-  <si>
-    <t>ΟΧΙ</t>
-  </si>
-  <si>
-    <t>Μέτρηση</t>
-  </si>
-  <si>
-    <t>SH(C350)-0000011811</t>
-  </si>
-  <si>
-    <t>ΚΩΣ</t>
-  </si>
-  <si>
-    <t>SH(C)-0000027883</t>
-  </si>
-  <si>
-    <t>001 Έδρα</t>
-  </si>
-  <si>
-    <t>ΨΥΓΕΙΟ</t>
-  </si>
-  <si>
-    <t>800585755</t>
-  </si>
-  <si>
-    <t>ΛΟΥΛΟΥΔΗ ΕΜΠΟΡΙΚΗ ΤΟΥΡΙΣΤΙΚΗ ΞΕΝΟΔΟΧΕΙΑΚΗ ΒΙΟΤΕΧΝΙΚΗ ΜΟΝΟΠΡΟΣΩΠΗ Ι Κ Ε</t>
-  </si>
-  <si>
-    <t>ΗΡ.ΠΟΛΥΤΕΧΝΕΙΟΥ&amp;Γ.ΕΥΣΤΑΘΙΟΥ</t>
-  </si>
-  <si>
-    <t>ΠΛΑΤΕΙΑ ΑΠΟΔΗΜΩΝ ΚΑΡΠΑΘΙΩΝ</t>
-  </si>
-  <si>
-    <t>ΠΗΓΑΔΙΑ</t>
+    <t>SH(C)-0000028599</t>
+  </si>
+  <si>
+    <t>801595967</t>
+  </si>
+  <si>
+    <t>RETAIL AND MORE ΑΕ</t>
+  </si>
+  <si>
+    <t>219. Λυκίας 1</t>
+  </si>
+  <si>
+    <t>Ν ΣΜΥΡΝΗ</t>
+  </si>
+  <si>
+    <t>ΚΑΤΑΨΥΞΗ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012476</t>
+  </si>
+  <si>
+    <t>216. ΕΛ.ΒΕΝΙΖΕΛΛΟΥ</t>
+  </si>
+  <si>
+    <t>ΝΕΑ ΣΜΥΡΝΗ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012475</t>
+  </si>
+  <si>
+    <t>215. Κουντουριώτη 6 &amp; Αλικαρνασσού</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012474</t>
+  </si>
+  <si>
+    <t>204. Αρτάκης 15</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028606</t>
+  </si>
+  <si>
+    <t>217. Αγ.Βασιλείου 25-27</t>
+  </si>
+  <si>
+    <t>ΑΓ. ΔΗΜΗΤΡΙΟΣ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012469</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012468</t>
+  </si>
+  <si>
+    <t>218. Γεωργίου Παπανδρέου 52</t>
+  </si>
+  <si>
+    <t>ΑΡΓΥΡΟΥΠΟΛΗ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028605</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012466</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028622</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028621</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028604</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028620</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028603</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028619</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019489</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019488</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019487</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019486</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019485</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028618</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019484</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028600</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028607</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019492</t>
+  </si>
+  <si>
+    <t>803083318</t>
+  </si>
+  <si>
+    <t>SARAVAS FOOD MARKET Ι Κ Ε</t>
+  </si>
+  <si>
+    <t>ΠΛΑΤΕΙΑ ΕΛΕΥΘΕΡΙΑΣ</t>
+  </si>
+  <si>
+    <t>ΠΑΛ ΦΩΚΑΙΑ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028602</t>
+  </si>
+  <si>
+    <t>800462417</t>
+  </si>
+  <si>
+    <t>SPAR FOOD AND FUEL ΑΝΩΝΥΜΗ ΕΤΑΙΡΕΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΡΗΓΑ  ΦΕΡΑΙΟΥ  2  ΚΑΙ  Λ  ΠΟΣΕΙΔΩΝΟΣ</t>
+  </si>
+  <si>
+    <t>ΑΛΙΜΟΣ</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019481</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028601</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012467</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028609</t>
+  </si>
+  <si>
+    <t>801329179</t>
+  </si>
+  <si>
+    <t>ΑΦΟΙ ΜΑΡΗ ΚΑΙ ΣΙΑ ΕΤΕΡΟΡΡΥΘΜΗ ΕΤΑΙΡΕΙΑ</t>
+  </si>
+  <si>
+    <t>ΚΡΗΤΗΣ ΚΑΙ ΣΤΡΑΤΗΓΟΥ ΛΕΚΚΑ 40</t>
+  </si>
+  <si>
+    <t>ΜΑΡΟΥΣΙ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028608</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019480</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028610</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012470</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019479</t>
+  </si>
+  <si>
+    <t>802769750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΓΑΣΠΑΡΗ ΕΙΡΗΝΗ  ΒΕΛΙΩΤΗΣ ΣΤΑΥΡΟΣ Ο Ε</t>
+  </si>
+  <si>
+    <t>ΧΩΡΑ ΑΝΔΡΟΥ</t>
+  </si>
+  <si>
+    <t>ΑΝΔΡΟΣ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028597</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012478</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028595</t>
+  </si>
+  <si>
+    <t>039035330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΓΡΑΤΣΙΑ  ΕΙΡΗΝΗ ΔΕΜΕΝΕΟΣ</t>
+  </si>
+  <si>
+    <t>ΦΙΛΟΤΙ ΝΑΞΟΣ</t>
+  </si>
+  <si>
+    <t>ΧΑΡΑΥΓΗ ΔΟΝΟΥΣΗΣ</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019474</t>
+  </si>
+  <si>
+    <t>997136067</t>
+  </si>
+  <si>
+    <t>ΔΗΜΗΤΡΑΚΙΟΥ ΔΗΜΗΤΡΙΟΣ ΚΑΙ ΣΙΑ ΕΕ</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012477</t>
+  </si>
+  <si>
+    <t>090070164</t>
+  </si>
+  <si>
+    <t>ΔΙΚΕΜΣ ΔΙΟΙΚΗΣΗ ΚΕΝΤΡΩΝ ΕΦΟΔΙΑΣΜΟΥ ΜΟΝΑΔΩΝ ΣΤΡΑΤΟΥ</t>
+  </si>
+  <si>
+    <t>ΣΤΡΑΤΟΠΕΔΟ ΚΑΡΑΪΣΚΑΚΗ Β΄ -</t>
+  </si>
+  <si>
+    <t>ΣΤΡΑΤΟΠΕΔΟ ΚΑΡΑΪΣΚΑΚΗ Β΄</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028625</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019483</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019482</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028626</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028628</t>
+  </si>
+  <si>
+    <t>130500567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔΟΥΚΑΣ  ΝΙΚΟΛΑΟΣ ΕΥΑΓΓΕΛΟΣ</t>
+  </si>
+  <si>
+    <t>Λ ΜΑΡΑΘΩΝΟΣ 37ΧΛΜ</t>
+  </si>
+  <si>
+    <t>ΣΧΙΝΙΑΣ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028629</t>
+  </si>
+  <si>
+    <t>Ακυρωμένη</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028627</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012462</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019490</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028624</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028623</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028592</t>
+  </si>
+  <si>
+    <t>800558765</t>
+  </si>
+  <si>
+    <t>ΚΕΝΤΡΟ ΔΙΑΝΟΜΗΣ ΤΡΟΦΙΜΩΝ ΜΟΝ. Ι.Κ.Ε.</t>
+  </si>
+  <si>
+    <t>ΓΑΙΤΑΝΙ ΖΑΚΥΝΘΟΥ</t>
+  </si>
+  <si>
+    <t>ΨΑΡΟΥ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012461</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028593</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028591</t>
+  </si>
+  <si>
+    <t>2956</t>
+  </si>
+  <si>
+    <t>ΚΕΡΚΕΤΕΥΣ ΑΝΩΝΥΜΗ ΕΜΠΟΡΙΚΗ ΚΑΙ ΒΙΟΜΗΧΑΝΙΚΗ ΕΤΑΙΡΕΙ</t>
+  </si>
+  <si>
+    <t>ΤΡΕΙΣ ΕΚΚΛΗΣΙΕΣ</t>
+  </si>
+  <si>
+    <t>ΨΙΛΗ ΑΜΜΟΣ</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019478</t>
+  </si>
+  <si>
+    <t>046938415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΜΑΡΗΣ  ΙΩΑΝΝΗΣ ΕΥΑΓΓΕΛΟΣ</t>
+  </si>
+  <si>
+    <t>ΑΓ ΑΝΑΡΓΥΡΩΝ 32</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028614</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028615</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028616</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012472</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019491</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>ΜΑΡΙΑ ΚΑΙ ΜΙΧΑΗΛΙΑ ΒΗΧΟΥ ΟΕ</t>
+  </si>
+  <si>
+    <t>ΑΔΑΜΑΝΤΑΣ</t>
+  </si>
+  <si>
+    <t>ΜΗΛΟΣ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028596</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012471</t>
+  </si>
+  <si>
+    <t>100249877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΝΕΖΗ  ΚΥΡΙΑΚΗ ΣΩΤΗΡΙΟΣ</t>
+  </si>
+  <si>
+    <t>ΒΟΡΕΙΟΥ ΗΠΕΙΡΟΥ 4</t>
+  </si>
+  <si>
+    <t>ΚΑΜΑΤΕΡΟ</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019477</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028612</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019476</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028613</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028611</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019475</t>
+  </si>
+  <si>
+    <t>998716895</t>
+  </si>
+  <si>
+    <t>Π ΚΑΙ Ν ΓΡΑΜΜΑΤΙΚΑΚΗΣ ΚΑΙ ΣΙΑ ΕΕ</t>
+  </si>
+  <si>
+    <t>ΜΟΛΑΟΙ ΛΑΚΩΝΙΑΣ</t>
+  </si>
+  <si>
+    <t>ΣΥΚΕΑ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012473</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028617</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012465</t>
+  </si>
+  <si>
+    <t>999874416</t>
+  </si>
+  <si>
+    <t>ΠΑΠΠΟΥ Γ. ΙΩΑΝΝΗΣ Α.Ε.</t>
+  </si>
+  <si>
+    <t>ΛΕΩΦ.ΗΡΑΚΛΕΙΔΩΝ 77- ΙΑΛΥΣΟΣ</t>
+  </si>
+  <si>
+    <t>ΤΡΙΑΝΤΑ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028598</t>
+  </si>
+  <si>
+    <t>802660976</t>
+  </si>
+  <si>
+    <t>ΠΕΝΤΕΛΙΚΟ Ε Ε</t>
+  </si>
+  <si>
+    <t>ΕΡΜΟΥ</t>
+  </si>
+  <si>
+    <t>Π ΠΕΝΤΕΛΗ</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012463</t>
+  </si>
+  <si>
+    <t>800156819</t>
+  </si>
+  <si>
+    <t>ΠΟΛΙΤΗΣ ΤΡΟΦΟΔΟΤΙΚΗ ΚΕΑΣ ΑΝΩΝΥΜΗ ΕΤΑΙΡΕΙΑ</t>
+  </si>
+  <si>
+    <t>ΕΠΑΡΧΙΑΚΗ ΟΔΟΣ ΚΟΡΗΣΣΙΑΣ ΙΟΥΛΙΔΟΣ</t>
+  </si>
+  <si>
+    <t>ΧΑΒΟΥΝΑ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028589</t>
+  </si>
+  <si>
+    <t>997461675</t>
+  </si>
+  <si>
+    <t>ΣΑΡΑΒΑΣ FOOD MARKET ΟΕ</t>
+  </si>
+  <si>
+    <t>ΜΥΚΟΝΟΥ 2-4</t>
+  </si>
+  <si>
+    <t>ΧΟΛΑΡΓΟΣ</t>
+  </si>
+  <si>
+    <t>SH(C)-0000028590</t>
+  </si>
+  <si>
+    <t>SH(C350)-0000012460</t>
+  </si>
+  <si>
+    <t>997246152</t>
+  </si>
+  <si>
+    <t>ΤΖΑΜΠΟ ΤΖΕΤ ΝΑΥΤΙΚΗ ΕΤΑΙΡΕΙΑ (SEAJET)</t>
+  </si>
+  <si>
+    <t>ΠΥΛΗ E9</t>
+  </si>
+  <si>
+    <t>ΠΕΙΡΑΙΑΣ</t>
+  </si>
+  <si>
+    <t>SH(C340)-0000019473</t>
   </si>
 </sst>
 </file>
@@ -122,7 +612,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.##"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,21 +624,11 @@
       <sz val="8.25"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="161"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="161"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="161"/>
     </font>
   </fonts>
   <fills count="7">
@@ -165,28 +645,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9A9A9"/>
+        <fgColor rgb="FFFFE0C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC0C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFA9A9A9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -261,64 +739,53 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -365,7 +832,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -400,7 +867,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -577,251 +1044,3962 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="86.28515625" customWidth="1"/>
-    <col min="7" max="7" width="40.42578125" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
-    <col min="11" max="11" width="21.28515625" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.86" customWidth="1"/>
+    <col min="2" max="2" width="21.57" customWidth="1"/>
+    <col min="3" max="3" width="22.43" customWidth="1"/>
+    <col min="4" max="4" width="17.43" customWidth="1"/>
+    <col min="5" max="5" width="14.57" customWidth="1"/>
+    <col min="6" max="6" width="63.86" customWidth="1"/>
+    <col min="7" max="7" width="40.43" customWidth="1"/>
+    <col min="8" max="8" width="30.14" customWidth="1"/>
+    <col min="9" max="9" width="12.14" customWidth="1"/>
+    <col min="10" max="10" width="15.57" customWidth="1"/>
+    <col min="11" max="11" width="21.29" customWidth="1"/>
+    <col min="12" max="12" width="14.86" customWidth="1"/>
+    <col min="13" max="13" width="12.14" customWidth="1"/>
+    <col min="14" max="14" width="21.71" customWidth="1"/>
+    <col min="15" max="15" width="17.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="44.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="44.25" customHeight="1">
+      <c t="s" r="A1" s="1">
+        <v>0</v>
+      </c>
+      <c t="s" r="B1" s="1">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c t="s" r="C1" s="1">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c t="s" r="D1" s="1">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c t="s" r="E1" s="1">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c t="s" r="F1" s="1">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c t="s" r="G1" s="1">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c t="s" r="H1" s="1">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c t="s" r="I1" s="1">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c t="s" r="J1" s="1">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c t="s" r="K1" s="1">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c t="s" r="L1" s="1">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c t="s" r="M1" s="1">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c t="s" r="N1" s="1">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c t="s" r="O1" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c t="s" r="A2" s="2">
+        <v>15</v>
+      </c>
+      <c t="s" r="B2" s="2">
         <v>16</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c t="s" r="C2" s="2">
         <v>17</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c t="s" r="D2" s="2">
         <v>18</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c t="s" r="E2" s="2">
+        <v>19</v>
+      </c>
+      <c t="s" r="F2" s="2">
+        <v>20</v>
+      </c>
+      <c t="s" r="G2" s="2">
+        <v>21</v>
+      </c>
+      <c t="s" r="H2" s="2">
+        <v>22</v>
+      </c>
+      <c t="s" r="I2" s="2">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>41</v>
+      </c>
+      <c r="L2" s="3">
+        <v>46</v>
+      </c>
+      <c r="M2" s="3">
+        <v>36</v>
+      </c>
+      <c t="s" r="N2" s="2">
+        <v>24</v>
+      </c>
+      <c r="O2" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c t="s" r="A3" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B3" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C3" s="4">
+        <v>26</v>
+      </c>
+      <c t="s" r="D3" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E3" s="4">
+        <v>19</v>
+      </c>
+      <c t="s" r="F3" s="4">
+        <v>20</v>
+      </c>
+      <c t="s" r="G3" s="4">
+        <v>21</v>
+      </c>
+      <c t="s" r="H3" s="4">
+        <v>22</v>
+      </c>
+      <c t="s" r="I3" s="4">
+        <v>23</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N3" s="4">
+        <v>24</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c t="s" r="A4" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B4" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C4" s="4">
         <v>28</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c t="s" r="D4" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E4" s="4">
+        <v>19</v>
+      </c>
+      <c t="s" r="F4" s="4">
+        <v>20</v>
+      </c>
+      <c t="s" r="G4" s="4">
+        <v>21</v>
+      </c>
+      <c t="s" r="H4" s="4">
+        <v>22</v>
+      </c>
+      <c t="s" r="I4" s="4">
+        <v>29</v>
+      </c>
+      <c r="J4" s="5">
+        <v>265</v>
+      </c>
+      <c r="K4" s="5">
+        <v>266</v>
+      </c>
+      <c r="L4" s="5">
+        <v>305</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c t="s" r="N4" s="4">
+        <v>24</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c t="s" r="A5" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B5" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C5" s="4">
+        <v>30</v>
+      </c>
+      <c t="s" r="D5" s="4">
         <v>31</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c t="s" r="E5" s="4">
         <v>19</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c t="s" r="F5" s="4">
         <v>20</v>
       </c>
-      <c r="J2" s="10">
-        <v>0</v>
-      </c>
-      <c r="K2" s="10">
+      <c t="s" r="G5" s="4">
+        <v>21</v>
+      </c>
+      <c t="s" r="H5" s="4">
+        <v>22</v>
+      </c>
+      <c t="s" r="I5" s="4">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5">
+        <v>52</v>
+      </c>
+      <c r="K5" s="5">
+        <v>52</v>
+      </c>
+      <c r="L5" s="5">
+        <v>65</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N5" s="4">
+        <v>24</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c t="s" r="A6" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B6" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C6" s="4">
+        <v>32</v>
+      </c>
+      <c t="s" r="D6" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E6" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F6" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G6" s="4">
+        <v>35</v>
+      </c>
+      <c t="s" r="H6" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I6" s="4">
+        <v>37</v>
+      </c>
+      <c r="J6" s="5">
         <v>3</v>
       </c>
-      <c r="L2" s="10">
+      <c r="K6" s="5">
         <v>3</v>
       </c>
-      <c r="M2" s="10">
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N6" s="4">
+        <v>24</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c t="s" r="A7" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B7" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C7" s="4">
+        <v>38</v>
+      </c>
+      <c t="s" r="D7" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E7" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F7" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G7" s="4">
+        <v>39</v>
+      </c>
+      <c t="s" r="H7" s="4">
+        <v>40</v>
+      </c>
+      <c t="s" r="I7" s="4">
+        <v>29</v>
+      </c>
+      <c r="J7" s="5">
+        <v>14</v>
+      </c>
+      <c r="K7" s="5">
+        <v>14</v>
+      </c>
+      <c r="L7" s="5">
+        <v>15</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N7" s="4">
+        <v>24</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c t="s" r="A8" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B8" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C8" s="4">
+        <v>41</v>
+      </c>
+      <c t="s" r="D8" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E8" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F8" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G8" s="4">
+        <v>42</v>
+      </c>
+      <c t="s" r="H8" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I8" s="4">
+        <v>29</v>
+      </c>
+      <c r="J8" s="5">
+        <v>13</v>
+      </c>
+      <c r="K8" s="5">
+        <v>13</v>
+      </c>
+      <c r="L8" s="5">
+        <v>15</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N8" s="4">
+        <v>24</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c t="s" r="A9" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B9" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C9" s="4">
+        <v>43</v>
+      </c>
+      <c t="s" r="D9" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E9" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F9" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G9" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="H9" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I9" s="4">
+        <v>29</v>
+      </c>
+      <c r="J9" s="5">
+        <v>11</v>
+      </c>
+      <c r="K9" s="5">
+        <v>11</v>
+      </c>
+      <c r="L9" s="5">
+        <v>11</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N9" s="4">
+        <v>24</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c t="s" r="A10" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B10" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C10" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="D10" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E10" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F10" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G10" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="H10" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="I10" s="4">
+        <v>37</v>
+      </c>
+      <c r="J10" s="5">
+        <v>11</v>
+      </c>
+      <c r="K10" s="5">
+        <v>11</v>
+      </c>
+      <c r="L10" s="5">
+        <v>14</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N10" s="4">
+        <v>24</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c t="s" r="A11" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B11" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C11" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="D11" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E11" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F11" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G11" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="H11" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="I11" s="4">
+        <v>29</v>
+      </c>
+      <c r="J11" s="5">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5">
+        <v>10</v>
+      </c>
+      <c r="L11" s="5">
+        <v>11</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N11" s="4">
+        <v>24</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c t="s" r="A12" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B12" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C12" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="D12" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E12" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F12" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G12" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="H12" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="I12" s="4">
+        <v>29</v>
+      </c>
+      <c r="J12" s="5">
+        <v>5</v>
+      </c>
+      <c r="K12" s="5">
+        <v>5</v>
+      </c>
+      <c r="L12" s="5">
+        <v>5</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N12" s="4">
+        <v>24</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c t="s" r="A13" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B13" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C13" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="D13" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E13" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F13" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G13" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="H13" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="I13" s="4">
+        <v>37</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N13" s="4">
+        <v>24</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c t="s" r="A14" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B14" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C14" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="D14" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E14" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F14" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G14" s="4">
+        <v>35</v>
+      </c>
+      <c t="s" r="H14" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I14" s="4">
+        <v>29</v>
+      </c>
+      <c r="J14" s="5">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5">
+        <v>6</v>
+      </c>
+      <c r="L14" s="5">
+        <v>6</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N14" s="4">
+        <v>24</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c t="s" r="A15" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B15" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C15" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="D15" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E15" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F15" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G15" s="4">
+        <v>39</v>
+      </c>
+      <c t="s" r="H15" s="4">
+        <v>40</v>
+      </c>
+      <c t="s" r="I15" s="4">
+        <v>37</v>
+      </c>
+      <c r="J15" s="5">
+        <v>10</v>
+      </c>
+      <c r="K15" s="5">
+        <v>10</v>
+      </c>
+      <c r="L15" s="5">
+        <v>15</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N15" s="4">
+        <v>24</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c t="s" r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B16" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C16" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="D16" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E16" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F16" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G16" s="4">
+        <v>39</v>
+      </c>
+      <c t="s" r="H16" s="4">
+        <v>40</v>
+      </c>
+      <c t="s" r="I16" s="4">
+        <v>23</v>
+      </c>
+      <c r="J16" s="5">
+        <v>10</v>
+      </c>
+      <c r="K16" s="5">
+        <v>10</v>
+      </c>
+      <c r="L16" s="5">
+        <v>14</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N16" s="4">
+        <v>24</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c t="s" r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B17" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C17" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="D17" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E17" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F17" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G17" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="H17" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="I17" s="4">
+        <v>29</v>
+      </c>
+      <c r="J17" s="5">
+        <v>2</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N17" s="4">
+        <v>24</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c t="s" r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B18" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C18" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="D18" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E18" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F18" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G18" s="4">
+        <v>42</v>
+      </c>
+      <c t="s" r="H18" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I18" s="4">
+        <v>37</v>
+      </c>
+      <c r="J18" s="5">
+        <v>8</v>
+      </c>
+      <c r="K18" s="5">
+        <v>8</v>
+      </c>
+      <c r="L18" s="5">
+        <v>8</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N18" s="4">
+        <v>24</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c t="s" r="A19" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B19" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C19" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="D19" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E19" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F19" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G19" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="H19" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="I19" s="4">
+        <v>23</v>
+      </c>
+      <c r="J19" s="5">
+        <v>2</v>
+      </c>
+      <c r="K19" s="5">
+        <v>2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N19" s="4">
+        <v>24</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c t="s" r="A20" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B20" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C20" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="D20" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E20" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F20" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G20" s="4">
+        <v>42</v>
+      </c>
+      <c t="s" r="H20" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I20" s="4">
+        <v>23</v>
+      </c>
+      <c r="J20" s="5">
+        <v>9</v>
+      </c>
+      <c r="K20" s="5">
+        <v>9</v>
+      </c>
+      <c r="L20" s="5">
+        <v>9</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N20" s="4">
+        <v>24</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c t="s" r="A21" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B21" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C21" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="D21" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E21" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F21" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G21" s="4">
+        <v>39</v>
+      </c>
+      <c t="s" r="H21" s="4">
+        <v>40</v>
+      </c>
+      <c t="s" r="I21" s="4">
+        <v>29</v>
+      </c>
+      <c r="J21" s="5">
+        <v>80</v>
+      </c>
+      <c r="K21" s="5">
+        <v>80</v>
+      </c>
+      <c r="L21" s="5">
+        <v>89</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N21" s="4">
+        <v>24</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c t="s" r="A22" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B22" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C22" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="D22" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E22" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F22" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G22" s="4">
+        <v>42</v>
+      </c>
+      <c t="s" r="H22" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I22" s="4">
+        <v>29</v>
+      </c>
+      <c r="J22" s="5">
+        <v>36</v>
+      </c>
+      <c r="K22" s="5">
+        <v>36</v>
+      </c>
+      <c r="L22" s="5">
+        <v>44</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N22" s="4">
+        <v>24</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c t="s" r="A23" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B23" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C23" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="D23" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E23" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F23" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G23" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="H23" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I23" s="4">
+        <v>29</v>
+      </c>
+      <c r="J23" s="5">
+        <v>46</v>
+      </c>
+      <c r="K23" s="5">
+        <v>46</v>
+      </c>
+      <c r="L23" s="5">
+        <v>56</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N23" s="4">
+        <v>24</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c t="s" r="A24" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B24" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C24" s="4">
+        <v>63</v>
+      </c>
+      <c t="s" r="D24" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E24" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F24" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G24" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="H24" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="I24" s="4">
+        <v>29</v>
+      </c>
+      <c r="J24" s="5">
+        <v>51</v>
+      </c>
+      <c r="K24" s="5">
+        <v>51</v>
+      </c>
+      <c r="L24" s="5">
+        <v>58</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N24" s="4">
+        <v>24</v>
+      </c>
+      <c r="O24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c t="s" r="A25" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B25" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C25" s="4">
+        <v>64</v>
+      </c>
+      <c t="s" r="D25" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E25" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F25" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G25" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="H25" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="I25" s="4">
+        <v>29</v>
+      </c>
+      <c r="J25" s="5">
+        <v>22</v>
+      </c>
+      <c r="K25" s="5">
+        <v>22</v>
+      </c>
+      <c r="L25" s="5">
+        <v>24</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N25" s="4">
+        <v>24</v>
+      </c>
+      <c r="O25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c t="s" r="A26" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B26" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C26" s="4">
+        <v>65</v>
+      </c>
+      <c t="s" r="D26" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E26" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F26" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G26" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="H26" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I26" s="4">
+        <v>37</v>
+      </c>
+      <c r="J26" s="5">
         <v>3</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="K26" s="5">
+        <v>3</v>
+      </c>
+      <c r="L26" s="5">
+        <v>4</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N26" s="4">
+        <v>24</v>
+      </c>
+      <c r="O26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c t="s" r="A27" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B27" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C27" s="4">
+        <v>66</v>
+      </c>
+      <c t="s" r="D27" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E27" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F27" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G27" s="4">
+        <v>35</v>
+      </c>
+      <c t="s" r="H27" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I27" s="4">
+        <v>29</v>
+      </c>
+      <c r="J27" s="5">
+        <v>27</v>
+      </c>
+      <c r="K27" s="5">
+        <v>27</v>
+      </c>
+      <c r="L27" s="5">
+        <v>29</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N27" s="4">
+        <v>24</v>
+      </c>
+      <c r="O27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c t="s" r="A28" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B28" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C28" s="4">
+        <v>67</v>
+      </c>
+      <c t="s" r="D28" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E28" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F28" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G28" s="4">
+        <v>35</v>
+      </c>
+      <c t="s" r="H28" s="4">
+        <v>36</v>
+      </c>
+      <c t="s" r="I28" s="4">
+        <v>23</v>
+      </c>
+      <c r="J28" s="5">
+        <v>2</v>
+      </c>
+      <c r="K28" s="5">
+        <v>2</v>
+      </c>
+      <c r="L28" s="5">
+        <v>2</v>
+      </c>
+      <c r="M28" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N28" s="4">
+        <v>24</v>
+      </c>
+      <c r="O28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c t="s" r="A29" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B29" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C29" s="4">
+        <v>68</v>
+      </c>
+      <c t="s" r="D29" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E29" s="4">
+        <v>33</v>
+      </c>
+      <c t="s" r="F29" s="4">
+        <v>34</v>
+      </c>
+      <c t="s" r="G29" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="H29" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="I29" s="4">
+        <v>23</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <v>1</v>
+      </c>
+      <c r="L29" s="5">
+        <v>1</v>
+      </c>
+      <c r="M29" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N29" s="4">
+        <v>24</v>
+      </c>
+      <c r="O29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c t="s" r="A30" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B30" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C30" s="4">
+        <v>69</v>
+      </c>
+      <c t="s" r="D30" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E30" s="4">
+        <v>70</v>
+      </c>
+      <c t="s" r="F30" s="4">
+        <v>71</v>
+      </c>
+      <c t="s" r="G30" s="4">
+        <v>72</v>
+      </c>
+      <c t="s" r="H30" s="4">
+        <v>73</v>
+      </c>
+      <c t="s" r="I30" s="4">
+        <v>29</v>
+      </c>
+      <c r="J30" s="5">
+        <v>4</v>
+      </c>
+      <c r="K30" s="5">
+        <v>4</v>
+      </c>
+      <c r="L30" s="5">
+        <v>4</v>
+      </c>
+      <c r="M30" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N30" s="4">
+        <v>24</v>
+      </c>
+      <c r="O30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c t="s" r="A31" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B31" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C31" s="4">
+        <v>74</v>
+      </c>
+      <c t="s" r="D31" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E31" s="4">
+        <v>75</v>
+      </c>
+      <c t="s" r="F31" s="4">
+        <v>76</v>
+      </c>
+      <c t="s" r="G31" s="4">
+        <v>77</v>
+      </c>
+      <c t="s" r="H31" s="4">
+        <v>78</v>
+      </c>
+      <c t="s" r="I31" s="4">
+        <v>29</v>
+      </c>
+      <c r="J31" s="5">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5">
+        <v>1</v>
+      </c>
+      <c r="M31" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N31" s="4">
+        <v>24</v>
+      </c>
+      <c r="O31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c t="s" r="A32" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B32" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C32" s="4">
+        <v>79</v>
+      </c>
+      <c t="s" r="D32" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E32" s="4">
+        <v>75</v>
+      </c>
+      <c t="s" r="F32" s="4">
+        <v>76</v>
+      </c>
+      <c t="s" r="G32" s="4">
+        <v>77</v>
+      </c>
+      <c t="s" r="H32" s="4">
+        <v>78</v>
+      </c>
+      <c t="s" r="I32" s="4">
+        <v>29</v>
+      </c>
+      <c r="J32" s="5">
+        <v>47</v>
+      </c>
+      <c r="K32" s="5">
+        <v>47</v>
+      </c>
+      <c r="L32" s="5">
+        <v>50</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N32" s="4">
+        <v>24</v>
+      </c>
+      <c r="O32" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c t="s" r="A33" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B33" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C33" s="4">
+        <v>80</v>
+      </c>
+      <c t="s" r="D33" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E33" s="4">
+        <v>75</v>
+      </c>
+      <c t="s" r="F33" s="4">
+        <v>76</v>
+      </c>
+      <c t="s" r="G33" s="4">
+        <v>77</v>
+      </c>
+      <c t="s" r="H33" s="4">
+        <v>78</v>
+      </c>
+      <c t="s" r="I33" s="4">
+        <v>23</v>
+      </c>
+      <c r="J33" s="5">
+        <v>29</v>
+      </c>
+      <c r="K33" s="5">
+        <v>29</v>
+      </c>
+      <c r="L33" s="5">
+        <v>36</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N33" s="4">
+        <v>24</v>
+      </c>
+      <c r="O33" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c t="s" r="A34" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B34" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C34" s="4">
+        <v>81</v>
+      </c>
+      <c t="s" r="D34" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E34" s="4">
+        <v>75</v>
+      </c>
+      <c t="s" r="F34" s="4">
+        <v>76</v>
+      </c>
+      <c t="s" r="G34" s="4">
+        <v>77</v>
+      </c>
+      <c t="s" r="H34" s="4">
+        <v>78</v>
+      </c>
+      <c t="s" r="I34" s="4">
+        <v>29</v>
+      </c>
+      <c r="J34" s="5">
+        <v>19</v>
+      </c>
+      <c r="K34" s="5">
+        <v>19</v>
+      </c>
+      <c r="L34" s="5">
+        <v>19</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N34" s="4">
+        <v>24</v>
+      </c>
+      <c r="O34" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c t="s" r="A35" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B35" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C35" s="4">
+        <v>82</v>
+      </c>
+      <c t="s" r="D35" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E35" s="4">
+        <v>83</v>
+      </c>
+      <c t="s" r="F35" s="4">
+        <v>84</v>
+      </c>
+      <c t="s" r="G35" s="4">
+        <v>85</v>
+      </c>
+      <c t="s" r="H35" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I35" s="4">
+        <v>37</v>
+      </c>
+      <c r="J35" s="5">
+        <v>6</v>
+      </c>
+      <c r="K35" s="5">
+        <v>6</v>
+      </c>
+      <c r="L35" s="5">
+        <v>10</v>
+      </c>
+      <c r="M35" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N35" s="4">
+        <v>24</v>
+      </c>
+      <c r="O35" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c t="s" r="A36" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B36" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C36" s="4">
+        <v>87</v>
+      </c>
+      <c t="s" r="D36" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E36" s="4">
+        <v>83</v>
+      </c>
+      <c t="s" r="F36" s="4">
+        <v>84</v>
+      </c>
+      <c t="s" r="G36" s="4">
+        <v>85</v>
+      </c>
+      <c t="s" r="H36" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I36" s="4">
+        <v>23</v>
+      </c>
+      <c r="J36" s="5">
+        <v>19</v>
+      </c>
+      <c r="K36" s="5">
+        <v>19</v>
+      </c>
+      <c r="L36" s="5">
+        <v>31</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N36" s="4">
+        <v>24</v>
+      </c>
+      <c r="O36" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c t="s" r="A37" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B37" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C37" s="4">
+        <v>88</v>
+      </c>
+      <c t="s" r="D37" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E37" s="4">
+        <v>83</v>
+      </c>
+      <c t="s" r="F37" s="4">
+        <v>84</v>
+      </c>
+      <c t="s" r="G37" s="4">
+        <v>85</v>
+      </c>
+      <c t="s" r="H37" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I37" s="4">
+        <v>29</v>
+      </c>
+      <c r="J37" s="5">
+        <v>94</v>
+      </c>
+      <c r="K37" s="5">
+        <v>94</v>
+      </c>
+      <c r="L37" s="5">
+        <v>118</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N37" s="4">
+        <v>24</v>
+      </c>
+      <c r="O37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c t="s" r="A38" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B38" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C38" s="4">
+        <v>89</v>
+      </c>
+      <c t="s" r="D38" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E38" s="4">
+        <v>83</v>
+      </c>
+      <c t="s" r="F38" s="4">
+        <v>84</v>
+      </c>
+      <c t="s" r="G38" s="4">
+        <v>85</v>
+      </c>
+      <c t="s" r="H38" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I38" s="4">
+        <v>29</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>2</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N38" s="4">
+        <v>24</v>
+      </c>
+      <c r="O38" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c t="s" r="A39" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B39" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C39" s="4">
+        <v>90</v>
+      </c>
+      <c t="s" r="D39" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E39" s="4">
+        <v>83</v>
+      </c>
+      <c t="s" r="F39" s="4">
+        <v>84</v>
+      </c>
+      <c t="s" r="G39" s="4">
+        <v>85</v>
+      </c>
+      <c t="s" r="H39" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I39" s="4">
+        <v>29</v>
+      </c>
+      <c r="J39" s="5">
+        <v>24</v>
+      </c>
+      <c r="K39" s="5">
+        <v>29</v>
+      </c>
+      <c r="L39" s="5">
+        <v>40</v>
+      </c>
+      <c r="M39" s="5">
+        <v>5</v>
+      </c>
+      <c t="s" r="N39" s="4">
+        <v>24</v>
+      </c>
+      <c r="O39" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c t="s" r="A40" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B40" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C40" s="4">
+        <v>91</v>
+      </c>
+      <c t="s" r="D40" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E40" s="4">
+        <v>92</v>
+      </c>
+      <c t="s" r="F40" s="4">
+        <v>93</v>
+      </c>
+      <c t="s" r="G40" s="4">
+        <v>94</v>
+      </c>
+      <c t="s" r="H40" s="4">
+        <v>95</v>
+      </c>
+      <c t="s" r="I40" s="4">
+        <v>29</v>
+      </c>
+      <c r="J40" s="5">
+        <v>2</v>
+      </c>
+      <c r="K40" s="5">
+        <v>2</v>
+      </c>
+      <c r="L40" s="5">
+        <v>2</v>
+      </c>
+      <c r="M40" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N40" s="4">
+        <v>24</v>
+      </c>
+      <c r="O40" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c t="s" r="A41" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B41" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C41" s="4">
+        <v>96</v>
+      </c>
+      <c t="s" r="D41" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E41" s="4">
+        <v>92</v>
+      </c>
+      <c t="s" r="F41" s="4">
+        <v>93</v>
+      </c>
+      <c t="s" r="G41" s="4">
+        <v>94</v>
+      </c>
+      <c t="s" r="H41" s="4">
+        <v>95</v>
+      </c>
+      <c t="s" r="I41" s="4">
+        <v>23</v>
+      </c>
+      <c r="J41" s="5">
+        <v>2</v>
+      </c>
+      <c r="K41" s="5">
+        <v>2</v>
+      </c>
+      <c r="L41" s="5">
+        <v>2</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N41" s="4">
+        <v>24</v>
+      </c>
+      <c r="O41" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c t="s" r="A42" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B42" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C42" s="4">
+        <v>97</v>
+      </c>
+      <c t="s" r="D42" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E42" s="4">
+        <v>92</v>
+      </c>
+      <c t="s" r="F42" s="4">
+        <v>93</v>
+      </c>
+      <c t="s" r="G42" s="4">
+        <v>94</v>
+      </c>
+      <c t="s" r="H42" s="4">
+        <v>95</v>
+      </c>
+      <c t="s" r="I42" s="4">
+        <v>29</v>
+      </c>
+      <c r="J42" s="5">
+        <v>3</v>
+      </c>
+      <c r="K42" s="5">
+        <v>3</v>
+      </c>
+      <c r="L42" s="5">
+        <v>4</v>
+      </c>
+      <c r="M42" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N42" s="4">
+        <v>24</v>
+      </c>
+      <c r="O42" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c t="s" r="A43" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B43" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C43" s="4">
+        <v>98</v>
+      </c>
+      <c t="s" r="D43" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E43" s="4">
+        <v>99</v>
+      </c>
+      <c t="s" r="F43" s="4">
+        <v>100</v>
+      </c>
+      <c t="s" r="G43" s="4">
+        <v>101</v>
+      </c>
+      <c t="s" r="H43" s="4">
+        <v>102</v>
+      </c>
+      <c t="s" r="I43" s="4">
+        <v>37</v>
+      </c>
+      <c r="J43" s="5">
+        <v>50</v>
+      </c>
+      <c r="K43" s="5">
+        <v>50</v>
+      </c>
+      <c r="L43" s="5">
+        <v>71</v>
+      </c>
+      <c r="M43" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N43" s="4">
+        <v>24</v>
+      </c>
+      <c r="O43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c t="s" r="A44" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B44" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C44" s="4">
+        <v>103</v>
+      </c>
+      <c t="s" r="D44" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E44" s="4">
+        <v>104</v>
+      </c>
+      <c t="s" r="F44" s="4">
+        <v>105</v>
+      </c>
+      <c t="s" r="G44" s="4">
+        <v>106</v>
+      </c>
+      <c t="s" r="H44" s="4">
+        <v>22</v>
+      </c>
+      <c t="s" r="I44" s="4">
+        <v>29</v>
+      </c>
+      <c r="J44" s="5">
+        <v>208</v>
+      </c>
+      <c r="K44" s="5">
+        <v>274</v>
+      </c>
+      <c r="L44" s="5">
+        <v>294</v>
+      </c>
+      <c r="M44" s="5">
+        <v>66</v>
+      </c>
+      <c t="s" r="N44" s="4">
+        <v>24</v>
+      </c>
+      <c r="O44" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c t="s" r="A45" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B45" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C45" s="4">
+        <v>107</v>
+      </c>
+      <c t="s" r="D45" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E45" s="4">
+        <v>108</v>
+      </c>
+      <c t="s" r="F45" s="4">
+        <v>109</v>
+      </c>
+      <c t="s" r="G45" s="4">
+        <v>110</v>
+      </c>
+      <c t="s" r="H45" s="4">
+        <v>111</v>
+      </c>
+      <c t="s" r="I45" s="4">
+        <v>29</v>
+      </c>
+      <c r="J45" s="5">
+        <v>37</v>
+      </c>
+      <c r="K45" s="5">
+        <v>37</v>
+      </c>
+      <c r="L45" s="5">
+        <v>40</v>
+      </c>
+      <c r="M45" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N45" s="4">
+        <v>24</v>
+      </c>
+      <c r="O45" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c t="s" r="A46" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B46" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C46" s="4">
+        <v>112</v>
+      </c>
+      <c t="s" r="D46" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E46" s="4">
+        <v>108</v>
+      </c>
+      <c t="s" r="F46" s="4">
+        <v>109</v>
+      </c>
+      <c t="s" r="G46" s="4">
+        <v>110</v>
+      </c>
+      <c t="s" r="H46" s="4">
+        <v>111</v>
+      </c>
+      <c t="s" r="I46" s="4">
+        <v>23</v>
+      </c>
+      <c r="J46" s="5">
+        <v>48</v>
+      </c>
+      <c r="K46" s="5">
+        <v>48</v>
+      </c>
+      <c r="L46" s="5">
+        <v>64</v>
+      </c>
+      <c r="M46" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N46" s="4">
+        <v>24</v>
+      </c>
+      <c r="O46" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c t="s" r="A47" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B47" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C47" s="4">
+        <v>113</v>
+      </c>
+      <c t="s" r="D47" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E47" s="4">
+        <v>108</v>
+      </c>
+      <c t="s" r="F47" s="4">
+        <v>109</v>
+      </c>
+      <c t="s" r="G47" s="4">
+        <v>110</v>
+      </c>
+      <c t="s" r="H47" s="4">
+        <v>111</v>
+      </c>
+      <c t="s" r="I47" s="4">
+        <v>23</v>
+      </c>
+      <c r="J47" s="5">
+        <v>1</v>
+      </c>
+      <c r="K47" s="5">
+        <v>1</v>
+      </c>
+      <c r="L47" s="5">
+        <v>1</v>
+      </c>
+      <c r="M47" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N47" s="4">
+        <v>24</v>
+      </c>
+      <c r="O47" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c t="s" r="A48" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B48" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C48" s="4">
+        <v>114</v>
+      </c>
+      <c t="s" r="D48" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E48" s="4">
+        <v>108</v>
+      </c>
+      <c t="s" r="F48" s="4">
+        <v>109</v>
+      </c>
+      <c t="s" r="G48" s="4">
+        <v>110</v>
+      </c>
+      <c t="s" r="H48" s="4">
+        <v>111</v>
+      </c>
+      <c t="s" r="I48" s="4">
+        <v>29</v>
+      </c>
+      <c r="J48" s="5">
+        <v>173</v>
+      </c>
+      <c r="K48" s="5">
+        <v>173</v>
+      </c>
+      <c r="L48" s="5">
+        <v>198</v>
+      </c>
+      <c r="M48" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N48" s="4">
+        <v>24</v>
+      </c>
+      <c r="O48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c t="s" r="A49" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B49" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C49" s="4">
+        <v>115</v>
+      </c>
+      <c t="s" r="D49" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E49" s="4">
+        <v>108</v>
+      </c>
+      <c t="s" r="F49" s="4">
+        <v>109</v>
+      </c>
+      <c t="s" r="G49" s="4">
+        <v>110</v>
+      </c>
+      <c t="s" r="H49" s="4">
+        <v>111</v>
+      </c>
+      <c t="s" r="I49" s="4">
+        <v>37</v>
+      </c>
+      <c r="J49" s="5">
+        <v>10</v>
+      </c>
+      <c r="K49" s="5">
+        <v>10</v>
+      </c>
+      <c r="L49" s="5">
+        <v>10</v>
+      </c>
+      <c r="M49" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N49" s="4">
+        <v>24</v>
+      </c>
+      <c r="O49" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c t="s" r="A50" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B50" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C50" s="4">
+        <v>116</v>
+      </c>
+      <c t="s" r="D50" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E50" s="4">
+        <v>117</v>
+      </c>
+      <c t="s" r="F50" s="4">
+        <v>118</v>
+      </c>
+      <c t="s" r="G50" s="4">
+        <v>119</v>
+      </c>
+      <c t="s" r="H50" s="4">
+        <v>120</v>
+      </c>
+      <c t="s" r="I50" s="4">
+        <v>29</v>
+      </c>
+      <c r="J50" s="5">
+        <v>1</v>
+      </c>
+      <c r="K50" s="5">
+        <v>1</v>
+      </c>
+      <c r="L50" s="5">
+        <v>1</v>
+      </c>
+      <c r="M50" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N50" s="4">
+        <v>24</v>
+      </c>
+      <c r="O50" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c t="s" r="A51" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B51" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C51" s="4">
+        <v>121</v>
+      </c>
+      <c t="s" r="D51" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E51" s="4">
+        <v>117</v>
+      </c>
+      <c t="s" r="F51" s="4">
+        <v>118</v>
+      </c>
+      <c t="s" r="G51" s="4">
+        <v>119</v>
+      </c>
+      <c t="s" r="H51" s="4">
+        <v>120</v>
+      </c>
+      <c t="s" r="I51" s="4">
+        <v>29</v>
+      </c>
+      <c r="J51" s="5">
+        <v>1</v>
+      </c>
+      <c r="K51" s="5">
+        <v>1</v>
+      </c>
+      <c r="L51" s="5">
+        <v>1</v>
+      </c>
+      <c r="M51" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N51" s="4">
+        <v>24</v>
+      </c>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c t="s" r="A52" s="6">
+        <v>15</v>
+      </c>
+      <c t="s" r="B52" s="6">
+        <v>122</v>
+      </c>
+      <c t="s" r="C52" s="6">
+        <v>123</v>
+      </c>
+      <c t="s" r="D52" s="6">
+        <v>31</v>
+      </c>
+      <c t="s" r="E52" s="6">
+        <v>117</v>
+      </c>
+      <c t="s" r="F52" s="6">
+        <v>118</v>
+      </c>
+      <c t="s" r="G52" s="6">
+        <v>119</v>
+      </c>
+      <c t="s" r="H52" s="6">
+        <v>120</v>
+      </c>
+      <c t="s" r="I52" s="6">
+        <v>29</v>
+      </c>
+      <c r="J52" s="7">
+        <v>1</v>
+      </c>
+      <c r="K52" s="7">
+        <v>1</v>
+      </c>
+      <c r="L52" s="7">
+        <v>1</v>
+      </c>
+      <c r="M52" s="7">
+        <v>0</v>
+      </c>
+      <c t="s" r="N52" s="6">
+        <v>24</v>
+      </c>
+      <c r="O52" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c t="s" r="A53" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B53" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C53" s="4">
+        <v>124</v>
+      </c>
+      <c t="s" r="D53" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E53" s="4">
+        <v>117</v>
+      </c>
+      <c t="s" r="F53" s="4">
+        <v>118</v>
+      </c>
+      <c t="s" r="G53" s="4">
+        <v>119</v>
+      </c>
+      <c t="s" r="H53" s="4">
+        <v>120</v>
+      </c>
+      <c t="s" r="I53" s="4">
+        <v>29</v>
+      </c>
+      <c r="J53" s="5">
+        <v>30</v>
+      </c>
+      <c r="K53" s="5">
+        <v>30</v>
+      </c>
+      <c r="L53" s="5">
+        <v>39</v>
+      </c>
+      <c r="M53" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N53" s="4">
+        <v>24</v>
+      </c>
+      <c r="O53" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c t="s" r="A54" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B54" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C54" s="4">
+        <v>125</v>
+      </c>
+      <c t="s" r="D54" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E54" s="4">
+        <v>117</v>
+      </c>
+      <c t="s" r="F54" s="4">
+        <v>118</v>
+      </c>
+      <c t="s" r="G54" s="4">
+        <v>119</v>
+      </c>
+      <c t="s" r="H54" s="4">
+        <v>120</v>
+      </c>
+      <c t="s" r="I54" s="4">
+        <v>29</v>
+      </c>
+      <c r="J54" s="5">
+        <v>99</v>
+      </c>
+      <c r="K54" s="5">
+        <v>99</v>
+      </c>
+      <c r="L54" s="5">
+        <v>115</v>
+      </c>
+      <c r="M54" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N54" s="4">
+        <v>24</v>
+      </c>
+      <c r="O54" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c t="s" r="A55" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B55" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C55" s="4">
+        <v>126</v>
+      </c>
+      <c t="s" r="D55" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E55" s="4">
+        <v>117</v>
+      </c>
+      <c t="s" r="F55" s="4">
+        <v>118</v>
+      </c>
+      <c t="s" r="G55" s="4">
+        <v>119</v>
+      </c>
+      <c t="s" r="H55" s="4">
+        <v>120</v>
+      </c>
+      <c t="s" r="I55" s="4">
+        <v>29</v>
+      </c>
+      <c r="J55" s="5">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <v>1</v>
+      </c>
+      <c r="M55" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N55" s="4">
+        <v>24</v>
+      </c>
+      <c r="O55" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c t="s" r="A56" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B56" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C56" s="4">
+        <v>127</v>
+      </c>
+      <c t="s" r="D56" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E56" s="4">
+        <v>117</v>
+      </c>
+      <c t="s" r="F56" s="4">
+        <v>118</v>
+      </c>
+      <c t="s" r="G56" s="4">
+        <v>119</v>
+      </c>
+      <c t="s" r="H56" s="4">
+        <v>120</v>
+      </c>
+      <c t="s" r="I56" s="4">
+        <v>23</v>
+      </c>
+      <c r="J56" s="5">
+        <v>10</v>
+      </c>
+      <c r="K56" s="5">
+        <v>10</v>
+      </c>
+      <c r="L56" s="5">
+        <v>13</v>
+      </c>
+      <c r="M56" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N56" s="4">
+        <v>24</v>
+      </c>
+      <c r="O56" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c t="s" r="A57" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B57" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C57" s="4">
+        <v>128</v>
+      </c>
+      <c t="s" r="D57" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E57" s="4">
+        <v>129</v>
+      </c>
+      <c t="s" r="F57" s="4">
+        <v>130</v>
+      </c>
+      <c t="s" r="G57" s="4">
+        <v>131</v>
+      </c>
+      <c t="s" r="H57" s="4">
+        <v>132</v>
+      </c>
+      <c t="s" r="I57" s="4">
+        <v>23</v>
+      </c>
+      <c r="J57" s="5">
+        <v>6</v>
+      </c>
+      <c r="K57" s="5">
+        <v>6</v>
+      </c>
+      <c r="L57" s="5">
+        <v>8</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N57" s="4">
+        <v>24</v>
+      </c>
+      <c r="O57" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c t="s" r="A58" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B58" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C58" s="4">
+        <v>133</v>
+      </c>
+      <c t="s" r="D58" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E58" s="4">
+        <v>129</v>
+      </c>
+      <c t="s" r="F58" s="4">
+        <v>130</v>
+      </c>
+      <c t="s" r="G58" s="4">
+        <v>131</v>
+      </c>
+      <c t="s" r="H58" s="4">
+        <v>132</v>
+      </c>
+      <c t="s" r="I58" s="4">
+        <v>29</v>
+      </c>
+      <c r="J58" s="5">
+        <v>4</v>
+      </c>
+      <c r="K58" s="5">
+        <v>4</v>
+      </c>
+      <c r="L58" s="5">
+        <v>4</v>
+      </c>
+      <c r="M58" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N58" s="4">
+        <v>24</v>
+      </c>
+      <c r="O58" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c t="s" r="A59" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B59" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C59" s="4">
+        <v>134</v>
+      </c>
+      <c t="s" r="D59" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E59" s="4">
+        <v>129</v>
+      </c>
+      <c t="s" r="F59" s="4">
+        <v>130</v>
+      </c>
+      <c t="s" r="G59" s="4">
+        <v>131</v>
+      </c>
+      <c t="s" r="H59" s="4">
+        <v>132</v>
+      </c>
+      <c t="s" r="I59" s="4">
+        <v>29</v>
+      </c>
+      <c r="J59" s="5">
+        <v>1</v>
+      </c>
+      <c r="K59" s="5">
+        <v>1</v>
+      </c>
+      <c r="L59" s="5">
+        <v>1</v>
+      </c>
+      <c r="M59" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N59" s="4">
+        <v>24</v>
+      </c>
+      <c r="O59" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c t="s" r="A60" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B60" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C60" s="4">
+        <v>135</v>
+      </c>
+      <c t="s" r="D60" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E60" s="4">
+        <v>136</v>
+      </c>
+      <c t="s" r="F60" s="4">
+        <v>137</v>
+      </c>
+      <c t="s" r="G60" s="4">
+        <v>138</v>
+      </c>
+      <c t="s" r="H60" s="4">
+        <v>139</v>
+      </c>
+      <c t="s" r="I60" s="4">
+        <v>23</v>
+      </c>
+      <c r="J60" s="5">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <v>8</v>
+      </c>
+      <c r="M60" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N60" s="4">
+        <v>24</v>
+      </c>
+      <c r="O60" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c t="s" r="A61" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B61" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C61" s="4">
+        <v>140</v>
+      </c>
+      <c t="s" r="D61" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E61" s="4">
+        <v>141</v>
+      </c>
+      <c t="s" r="F61" s="4">
+        <v>142</v>
+      </c>
+      <c t="s" r="G61" s="4">
+        <v>143</v>
+      </c>
+      <c t="s" r="H61" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I61" s="4">
+        <v>29</v>
+      </c>
+      <c r="J61" s="5">
+        <v>50</v>
+      </c>
+      <c r="K61" s="5">
+        <v>50</v>
+      </c>
+      <c r="L61" s="5">
+        <v>70</v>
+      </c>
+      <c r="M61" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N61" s="4">
+        <v>24</v>
+      </c>
+      <c r="O61" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c t="s" r="A62" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B62" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C62" s="4">
+        <v>144</v>
+      </c>
+      <c t="s" r="D62" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E62" s="4">
+        <v>141</v>
+      </c>
+      <c t="s" r="F62" s="4">
+        <v>142</v>
+      </c>
+      <c t="s" r="G62" s="4">
+        <v>143</v>
+      </c>
+      <c t="s" r="H62" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I62" s="4">
+        <v>23</v>
+      </c>
+      <c r="J62" s="5">
+        <v>16</v>
+      </c>
+      <c r="K62" s="5">
+        <v>16</v>
+      </c>
+      <c r="L62" s="5">
+        <v>22</v>
+      </c>
+      <c r="M62" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N62" s="4">
+        <v>24</v>
+      </c>
+      <c r="O62" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c t="s" r="A63" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B63" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C63" s="4">
+        <v>145</v>
+      </c>
+      <c t="s" r="D63" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E63" s="4">
+        <v>141</v>
+      </c>
+      <c t="s" r="F63" s="4">
+        <v>142</v>
+      </c>
+      <c t="s" r="G63" s="4">
+        <v>143</v>
+      </c>
+      <c t="s" r="H63" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I63" s="4">
+        <v>37</v>
+      </c>
+      <c r="J63" s="5">
+        <v>4</v>
+      </c>
+      <c r="K63" s="5">
+        <v>4</v>
+      </c>
+      <c r="L63" s="5">
+        <v>6</v>
+      </c>
+      <c r="M63" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N63" s="4">
+        <v>24</v>
+      </c>
+      <c r="O63" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c t="s" r="A64" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B64" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C64" s="4">
+        <v>146</v>
+      </c>
+      <c t="s" r="D64" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E64" s="4">
+        <v>141</v>
+      </c>
+      <c t="s" r="F64" s="4">
+        <v>142</v>
+      </c>
+      <c t="s" r="G64" s="4">
+        <v>143</v>
+      </c>
+      <c t="s" r="H64" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I64" s="4">
+        <v>29</v>
+      </c>
+      <c r="J64" s="5">
+        <v>1</v>
+      </c>
+      <c r="K64" s="5">
+        <v>1</v>
+      </c>
+      <c r="L64" s="5">
+        <v>1</v>
+      </c>
+      <c r="M64" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N64" s="4">
+        <v>24</v>
+      </c>
+      <c r="O64" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c t="s" r="A65" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B65" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C65" s="4">
+        <v>147</v>
+      </c>
+      <c t="s" r="D65" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E65" s="4">
+        <v>141</v>
+      </c>
+      <c t="s" r="F65" s="4">
+        <v>142</v>
+      </c>
+      <c t="s" r="G65" s="4">
+        <v>143</v>
+      </c>
+      <c t="s" r="H65" s="4">
+        <v>86</v>
+      </c>
+      <c t="s" r="I65" s="4">
+        <v>29</v>
+      </c>
+      <c r="J65" s="5">
+        <v>15</v>
+      </c>
+      <c r="K65" s="5">
         <v>21</v>
       </c>
-      <c r="O2" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="L65" s="5">
+        <v>24</v>
+      </c>
+      <c r="M65" s="5">
+        <v>6</v>
+      </c>
+      <c t="s" r="N65" s="4">
+        <v>24</v>
+      </c>
+      <c r="O65" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c t="s" r="A66" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B66" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C66" s="4">
+        <v>148</v>
+      </c>
+      <c t="s" r="D66" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E66" s="4">
+        <v>149</v>
+      </c>
+      <c t="s" r="F66" s="4">
+        <v>150</v>
+      </c>
+      <c t="s" r="G66" s="4">
+        <v>151</v>
+      </c>
+      <c t="s" r="H66" s="4">
+        <v>152</v>
+      </c>
+      <c t="s" r="I66" s="4">
+        <v>29</v>
+      </c>
+      <c r="J66" s="5">
+        <v>1</v>
+      </c>
+      <c r="K66" s="5">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5">
+        <v>1</v>
+      </c>
+      <c r="M66" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N66" s="4">
+        <v>24</v>
+      </c>
+      <c r="O66" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c t="s" r="A67" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B67" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C67" s="4">
+        <v>153</v>
+      </c>
+      <c t="s" r="D67" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E67" s="4">
+        <v>149</v>
+      </c>
+      <c t="s" r="F67" s="4">
+        <v>150</v>
+      </c>
+      <c t="s" r="G67" s="4">
+        <v>151</v>
+      </c>
+      <c t="s" r="H67" s="4">
+        <v>152</v>
+      </c>
+      <c t="s" r="I67" s="4">
+        <v>29</v>
+      </c>
+      <c r="J67" s="5">
+        <v>4</v>
+      </c>
+      <c r="K67" s="5">
+        <v>4</v>
+      </c>
+      <c r="L67" s="5">
+        <v>5</v>
+      </c>
+      <c r="M67" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N67" s="4">
+        <v>24</v>
+      </c>
+      <c r="O67" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c t="s" r="A68" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B68" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C68" s="4">
+        <v>154</v>
+      </c>
+      <c t="s" r="D68" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E68" s="4">
+        <v>155</v>
+      </c>
+      <c t="s" r="F68" s="4">
+        <v>156</v>
+      </c>
+      <c t="s" r="G68" s="4">
+        <v>157</v>
+      </c>
+      <c t="s" r="H68" s="4">
+        <v>158</v>
+      </c>
+      <c t="s" r="I68" s="4">
+        <v>29</v>
+      </c>
+      <c r="J68" s="5">
+        <v>18</v>
+      </c>
+      <c r="K68" s="5">
+        <v>18</v>
+      </c>
+      <c r="L68" s="5">
+        <v>20</v>
+      </c>
+      <c r="M68" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N68" s="4">
+        <v>24</v>
+      </c>
+      <c r="O68" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c t="s" r="A69" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B69" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C69" s="4">
+        <v>159</v>
+      </c>
+      <c t="s" r="D69" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E69" s="4">
+        <v>155</v>
+      </c>
+      <c t="s" r="F69" s="4">
+        <v>156</v>
+      </c>
+      <c t="s" r="G69" s="4">
+        <v>157</v>
+      </c>
+      <c t="s" r="H69" s="4">
+        <v>158</v>
+      </c>
+      <c t="s" r="I69" s="4">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="J69" s="5">
+        <v>1</v>
+      </c>
+      <c r="K69" s="5">
+        <v>1</v>
+      </c>
+      <c r="L69" s="5">
+        <v>1</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N69" s="4">
+        <v>24</v>
+      </c>
+      <c r="O69" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c t="s" r="A70" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B70" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C70" s="4">
+        <v>160</v>
+      </c>
+      <c t="s" r="D70" s="4">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c t="s" r="E70" s="4">
+        <v>155</v>
+      </c>
+      <c t="s" r="F70" s="4">
+        <v>156</v>
+      </c>
+      <c t="s" r="G70" s="4">
+        <v>157</v>
+      </c>
+      <c t="s" r="H70" s="4">
+        <v>158</v>
+      </c>
+      <c t="s" r="I70" s="4">
+        <v>37</v>
+      </c>
+      <c r="J70" s="5">
+        <v>20</v>
+      </c>
+      <c r="K70" s="5">
+        <v>20</v>
+      </c>
+      <c r="L70" s="5">
+        <v>24</v>
+      </c>
+      <c r="M70" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N70" s="4">
+        <v>24</v>
+      </c>
+      <c r="O70" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c t="s" r="A71" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B71" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C71" s="4">
+        <v>161</v>
+      </c>
+      <c t="s" r="D71" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E71" s="4">
+        <v>155</v>
+      </c>
+      <c t="s" r="F71" s="4">
+        <v>156</v>
+      </c>
+      <c t="s" r="G71" s="4">
+        <v>157</v>
+      </c>
+      <c t="s" r="H71" s="4">
+        <v>158</v>
+      </c>
+      <c t="s" r="I71" s="4">
+        <v>29</v>
+      </c>
+      <c r="J71" s="5">
+        <v>91</v>
+      </c>
+      <c r="K71" s="5">
+        <v>150</v>
+      </c>
+      <c r="L71" s="5">
+        <v>179</v>
+      </c>
+      <c r="M71" s="5">
+        <v>57</v>
+      </c>
+      <c t="s" r="N71" s="4">
+        <v>24</v>
+      </c>
+      <c r="O71" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c t="s" r="A72" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B72" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C72" s="4">
+        <v>162</v>
+      </c>
+      <c t="s" r="D72" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E72" s="4">
+        <v>155</v>
+      </c>
+      <c t="s" r="F72" s="4">
+        <v>156</v>
+      </c>
+      <c t="s" r="G72" s="4">
+        <v>157</v>
+      </c>
+      <c t="s" r="H72" s="4">
+        <v>158</v>
+      </c>
+      <c t="s" r="I72" s="4">
+        <v>29</v>
+      </c>
+      <c r="J72" s="5">
+        <v>5</v>
+      </c>
+      <c r="K72" s="5">
+        <v>5</v>
+      </c>
+      <c r="L72" s="5">
+        <v>5</v>
+      </c>
+      <c r="M72" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N72" s="4">
+        <v>24</v>
+      </c>
+      <c r="O72" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c t="s" r="A73" s="2">
+        <v>15</v>
+      </c>
+      <c t="s" r="B73" s="2">
+        <v>16</v>
+      </c>
+      <c t="s" r="C73" s="2">
+        <v>163</v>
+      </c>
+      <c t="s" r="D73" s="2">
+        <v>18</v>
+      </c>
+      <c t="s" r="E73" s="2">
+        <v>155</v>
+      </c>
+      <c t="s" r="F73" s="2">
+        <v>156</v>
+      </c>
+      <c t="s" r="G73" s="2">
+        <v>157</v>
+      </c>
+      <c t="s" r="H73" s="2">
+        <v>158</v>
+      </c>
+      <c t="s" r="I73" s="2">
+        <v>23</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3">
+        <v>35</v>
+      </c>
+      <c r="L73" s="3">
+        <v>43</v>
+      </c>
+      <c r="M73" s="3">
         <v>32</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="10">
-        <v>8</v>
-      </c>
-      <c r="K3" s="10">
-        <v>21</v>
-      </c>
-      <c r="L3" s="10">
-        <v>24</v>
-      </c>
-      <c r="M3" s="10">
-        <v>12</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="10">
+      <c t="s" r="N73" s="2">
+        <v>24</v>
+      </c>
+      <c r="O73" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c t="s" r="A74" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B74" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C74" s="4">
+        <v>164</v>
+      </c>
+      <c t="s" r="D74" s="4">
+        <v>27</v>
+      </c>
+      <c t="s" r="E74" s="4">
+        <v>165</v>
+      </c>
+      <c t="s" r="F74" s="4">
+        <v>166</v>
+      </c>
+      <c t="s" r="G74" s="4">
+        <v>167</v>
+      </c>
+      <c t="s" r="H74" s="4">
+        <v>168</v>
+      </c>
+      <c t="s" r="I74" s="4">
+        <v>29</v>
+      </c>
+      <c r="J74" s="5">
+        <v>176</v>
+      </c>
+      <c r="K74" s="5">
+        <v>238</v>
+      </c>
+      <c r="L74" s="5">
+        <v>282</v>
+      </c>
+      <c r="M74" s="5">
+        <v>61</v>
+      </c>
+      <c t="s" r="N74" s="4">
+        <v>24</v>
+      </c>
+      <c r="O74" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="7" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c t="s" r="A75" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B75" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C75" s="4">
+        <v>169</v>
+      </c>
+      <c t="s" r="D75" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E75" s="4">
+        <v>165</v>
+      </c>
+      <c t="s" r="F75" s="4">
+        <v>166</v>
+      </c>
+      <c t="s" r="G75" s="4">
+        <v>167</v>
+      </c>
+      <c t="s" r="H75" s="4">
+        <v>168</v>
+      </c>
+      <c t="s" r="I75" s="4">
+        <v>29</v>
+      </c>
+      <c r="J75" s="5">
+        <v>39</v>
+      </c>
+      <c r="K75" s="5">
+        <v>39</v>
+      </c>
+      <c r="L75" s="5">
+        <v>48</v>
+      </c>
+      <c r="M75" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N75" s="4">
+        <v>24</v>
+      </c>
+      <c r="O75" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c t="s" r="A76" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B76" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C76" s="4">
+        <v>170</v>
+      </c>
+      <c t="s" r="D76" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E76" s="4">
+        <v>165</v>
+      </c>
+      <c t="s" r="F76" s="4">
+        <v>166</v>
+      </c>
+      <c t="s" r="G76" s="4">
+        <v>167</v>
+      </c>
+      <c t="s" r="H76" s="4">
+        <v>168</v>
+      </c>
+      <c t="s" r="I76" s="4">
+        <v>29</v>
+      </c>
+      <c r="J76" s="5">
+        <v>3</v>
+      </c>
+      <c r="K76" s="5">
+        <v>3</v>
+      </c>
+      <c r="L76" s="5">
+        <v>3</v>
+      </c>
+      <c r="M76" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N76" s="4">
+        <v>24</v>
+      </c>
+      <c r="O76" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c t="s" r="A77" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B77" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C77" s="4">
+        <v>171</v>
+      </c>
+      <c t="s" r="D77" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E77" s="4">
+        <v>172</v>
+      </c>
+      <c t="s" r="F77" s="4">
+        <v>173</v>
+      </c>
+      <c t="s" r="G77" s="4">
+        <v>174</v>
+      </c>
+      <c t="s" r="H77" s="4">
+        <v>175</v>
+      </c>
+      <c t="s" r="I77" s="4">
+        <v>29</v>
+      </c>
+      <c r="J77" s="5">
+        <v>17</v>
+      </c>
+      <c r="K77" s="5">
+        <v>17</v>
+      </c>
+      <c r="L77" s="5">
+        <v>35</v>
+      </c>
+      <c r="M77" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N77" s="4">
+        <v>24</v>
+      </c>
+      <c r="O77" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c t="s" r="A78" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B78" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C78" s="4">
+        <v>176</v>
+      </c>
+      <c t="s" r="D78" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E78" s="4">
+        <v>177</v>
+      </c>
+      <c t="s" r="F78" s="4">
+        <v>178</v>
+      </c>
+      <c t="s" r="G78" s="4">
+        <v>179</v>
+      </c>
+      <c t="s" r="H78" s="4">
+        <v>180</v>
+      </c>
+      <c t="s" r="I78" s="4">
+        <v>23</v>
+      </c>
+      <c r="J78" s="5">
+        <v>1</v>
+      </c>
+      <c r="K78" s="5">
+        <v>1</v>
+      </c>
+      <c r="L78" s="5">
+        <v>1</v>
+      </c>
+      <c r="M78" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N78" s="4">
+        <v>24</v>
+      </c>
+      <c r="O78" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c t="s" r="A79" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B79" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C79" s="4">
+        <v>181</v>
+      </c>
+      <c t="s" r="D79" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E79" s="4">
+        <v>182</v>
+      </c>
+      <c t="s" r="F79" s="4">
+        <v>183</v>
+      </c>
+      <c t="s" r="G79" s="4">
+        <v>184</v>
+      </c>
+      <c t="s" r="H79" s="4">
+        <v>185</v>
+      </c>
+      <c t="s" r="I79" s="4">
+        <v>29</v>
+      </c>
+      <c r="J79" s="5">
+        <v>1</v>
+      </c>
+      <c r="K79" s="5">
+        <v>1</v>
+      </c>
+      <c r="L79" s="5">
+        <v>1</v>
+      </c>
+      <c r="M79" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N79" s="4">
+        <v>24</v>
+      </c>
+      <c r="O79" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c t="s" r="A80" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B80" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C80" s="4">
+        <v>186</v>
+      </c>
+      <c t="s" r="D80" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E80" s="4">
+        <v>187</v>
+      </c>
+      <c t="s" r="F80" s="4">
+        <v>188</v>
+      </c>
+      <c t="s" r="G80" s="4">
+        <v>189</v>
+      </c>
+      <c t="s" r="H80" s="4">
+        <v>190</v>
+      </c>
+      <c t="s" r="I80" s="4">
+        <v>23</v>
+      </c>
+      <c r="J80" s="5">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5">
+        <v>1</v>
+      </c>
+      <c r="M80" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N80" s="4">
+        <v>24</v>
+      </c>
+      <c r="O80" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c t="s" r="A81" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B81" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C81" s="4">
+        <v>191</v>
+      </c>
+      <c t="s" r="D81" s="4">
+        <v>18</v>
+      </c>
+      <c t="s" r="E81" s="4">
+        <v>187</v>
+      </c>
+      <c t="s" r="F81" s="4">
+        <v>188</v>
+      </c>
+      <c t="s" r="G81" s="4">
+        <v>189</v>
+      </c>
+      <c t="s" r="H81" s="4">
+        <v>190</v>
+      </c>
+      <c t="s" r="I81" s="4">
+        <v>29</v>
+      </c>
+      <c r="J81" s="5">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5">
+        <v>1</v>
+      </c>
+      <c r="M81" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N81" s="4">
+        <v>24</v>
+      </c>
+      <c r="O81" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c t="s" r="A82" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B82" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C82" s="4">
+        <v>192</v>
+      </c>
+      <c t="s" r="D82" s="4">
+        <v>31</v>
+      </c>
+      <c t="s" r="E82" s="4">
+        <v>193</v>
+      </c>
+      <c t="s" r="F82" s="4">
+        <v>194</v>
+      </c>
+      <c t="s" r="G82" s="4">
+        <v>195</v>
+      </c>
+      <c t="s" r="H82" s="4">
+        <v>196</v>
+      </c>
+      <c t="s" r="I82" s="4">
+        <v>29</v>
+      </c>
+      <c r="J82" s="5">
+        <v>7</v>
+      </c>
+      <c r="K82" s="5">
+        <v>9</v>
+      </c>
+      <c r="L82" s="5">
+        <v>9</v>
+      </c>
+      <c r="M82" s="5">
+        <v>2</v>
+      </c>
+      <c t="s" r="N82" s="4">
+        <v>24</v>
+      </c>
+      <c r="O82" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c t="s" r="A83" s="4">
+        <v>15</v>
+      </c>
+      <c t="s" r="B83" s="4">
+        <v>25</v>
+      </c>
+      <c t="s" r="C83" s="4">
+        <v>197</v>
+      </c>
+      <c t="s" r="D83" s="4">
         <v>27</v>
       </c>
-      <c r="J4" s="10">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10">
-        <v>35</v>
-      </c>
-      <c r="L4" s="10">
-        <v>45</v>
-      </c>
-      <c r="M4" s="10">
-        <v>35</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="13.5" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="2">
-        <v>84</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="3">
-        <v>616</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c t="s" r="E83" s="4">
+        <v>193</v>
+      </c>
+      <c t="s" r="F83" s="4">
+        <v>194</v>
+      </c>
+      <c t="s" r="G83" s="4">
+        <v>195</v>
+      </c>
+      <c t="s" r="H83" s="4">
+        <v>196</v>
+      </c>
+      <c t="s" r="I83" s="4">
+        <v>29</v>
+      </c>
+      <c r="J83" s="5">
+        <v>9</v>
+      </c>
+      <c r="K83" s="5">
+        <v>9</v>
+      </c>
+      <c r="L83" s="5">
+        <v>9</v>
+      </c>
+      <c r="M83" s="5">
+        <v>0</v>
+      </c>
+      <c t="s" r="N83" s="4">
+        <v>24</v>
+      </c>
+      <c r="O83" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="13.5" customHeight="1">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="9">
+        <v>82</v>
+      </c>
+      <c r="G84" s="10"/>
+      <c r="H84" s="10"/>
+      <c r="I84" s="10"/>
+      <c r="J84" s="11">
+        <v>2111</v>
+      </c>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="N84" s="12"/>
+      <c r="O84" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="K84:O84"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
